--- a/artfynd/A 60833-2025 artfynd.xlsx
+++ b/artfynd/A 60833-2025 artfynd.xlsx
@@ -678,11 +678,11 @@
         <v>127939548</v>
       </c>
       <c r="B2" t="n">
-        <v>57686</v>
+        <v>57950</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">

--- a/artfynd/A 60833-2025 artfynd.xlsx
+++ b/artfynd/A 60833-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY2"/>
+  <dimension ref="A1:AZ2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -788,8 +793,16 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127939548</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/artfynd/A 60833-2025 artfynd.xlsx
+++ b/artfynd/A 60833-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ2"/>
+  <dimension ref="A1:AZ3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -680,10 +680,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>127939548</v>
+        <v>135784616</v>
       </c>
       <c r="B2" t="n">
-        <v>57950</v>
+        <v>80561</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -691,46 +691,37 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100049</v>
+        <v>6462</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
+          <t>(Spreng.) Tuck.</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Västra risåsvägen, Beten, Storsjö, Hjd</t>
+          <t>Putten, Hjd</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>408153</v>
+        <v>408133</v>
       </c>
       <c r="R2" t="n">
-        <v>6970967</v>
+        <v>6971019</v>
       </c>
       <c r="S2" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -754,22 +745,12 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2025-08-28</t>
-        </is>
-      </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>10:49</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2025-08-28</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>10:49</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -784,16 +765,137 @@
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Kent Moén</t>
+          <t>Alexander Singer</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Kent Moén</t>
+          <t>Alexander Singer</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
       <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135784616</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>127939548</v>
+      </c>
+      <c r="B3" t="n">
+        <v>57950</v>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E3" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>Västra risåsvägen, Beten, Storsjö, Hjd</t>
+        </is>
+      </c>
+      <c r="Q3" t="n">
+        <v>408153</v>
+      </c>
+      <c r="R3" t="n">
+        <v>6970967</v>
+      </c>
+      <c r="S3" t="n">
+        <v>50</v>
+      </c>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>Berg</t>
+        </is>
+      </c>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>Storsjö</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>2025-08-28</t>
+        </is>
+      </c>
+      <c r="Z3" t="inlineStr">
+        <is>
+          <t>10:49</t>
+        </is>
+      </c>
+      <c r="AA3" t="inlineStr">
+        <is>
+          <t>2025-08-28</t>
+        </is>
+      </c>
+      <c r="AB3" t="inlineStr">
+        <is>
+          <t>10:49</t>
+        </is>
+      </c>
+      <c r="AD3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT3" t="inlineStr"/>
+      <c r="AW3" t="inlineStr">
+        <is>
+          <t>Kent Moén</t>
+        </is>
+      </c>
+      <c r="AX3" t="inlineStr">
+        <is>
+          <t>Kent Moén</t>
+        </is>
+      </c>
+      <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
         <is>
           <t>https://artportalen.se/Sighting/127939548</t>
         </is>
@@ -802,6 +904,7 @@
   </sheetData>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 60833-2025 artfynd.xlsx
+++ b/artfynd/A 60833-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>135784616</v>
       </c>
       <c r="B2" t="n">
-        <v>80561</v>
+        <v>80563</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 60833-2025 artfynd.xlsx
+++ b/artfynd/A 60833-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>135784616</v>
       </c>
       <c r="B2" t="n">
-        <v>80563</v>
+        <v>80564</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 60833-2025 artfynd.xlsx
+++ b/artfynd/A 60833-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>135784616</v>
       </c>
       <c r="B2" t="n">
-        <v>80564</v>
+        <v>80565</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 60833-2025 artfynd.xlsx
+++ b/artfynd/A 60833-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>135784616</v>
       </c>
       <c r="B2" t="n">
-        <v>80565</v>
+        <v>80569</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 60833-2025 artfynd.xlsx
+++ b/artfynd/A 60833-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>135784616</v>
       </c>
       <c r="B2" t="n">
-        <v>80569</v>
+        <v>80570</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 60833-2025 artfynd.xlsx
+++ b/artfynd/A 60833-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>135784616</v>
       </c>
       <c r="B2" t="n">
-        <v>80570</v>
+        <v>80574</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 60833-2025 artfynd.xlsx
+++ b/artfynd/A 60833-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>135784616</v>
       </c>
       <c r="B2" t="n">
-        <v>80574</v>
+        <v>80580</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 60833-2025 artfynd.xlsx
+++ b/artfynd/A 60833-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ3"/>
+  <dimension ref="A1:AZ4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -898,6 +898,117 @@
       <c r="AZ3" t="inlineStr">
         <is>
           <t>https://artportalen.se/Sighting/127939548</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>136427850</v>
+      </c>
+      <c r="B4" t="n">
+        <v>58149</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>103023</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Tofsmes</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Lophophanes cristatus</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>stationär</t>
+        </is>
+      </c>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>Västra risåsvägen, Beten, Storsjö, Hjd</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>408117</v>
+      </c>
+      <c r="R4" t="n">
+        <v>6971138</v>
+      </c>
+      <c r="S4" t="n">
+        <v>10</v>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Berg</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Storsjö</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>2026-09-08</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>2026-09-08</t>
+        </is>
+      </c>
+      <c r="AD4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>Kent Moén</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>Kent Moén</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136427850</t>
         </is>
       </c>
     </row>
@@ -905,6 +1016,7 @@
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 60833-2025 artfynd.xlsx
+++ b/artfynd/A 60833-2025 artfynd.xlsx
@@ -906,7 +906,7 @@
         <v>136427850</v>
       </c>
       <c r="B4" t="n">
-        <v>58149</v>
+        <v>58162</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
